--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y34</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y33"/>
+  <dimension ref="A1:Y34"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -2970,10 +2970,87 @@
         <v>2026-09-04T16:15:00Z</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>DF-00033</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-09-09T15:20:59.000Z</v>
+      </c>
+      <c r="C34" t="str">
+        <v>EARLY ACCESS: New Listing 1917, Specialty Craft Beer, Wine &amp; Spirits Retailer in RI</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Baystate Business Brokers &lt;admin@baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Unknown ("Listing 1917" - specialty craft beer, wine &amp; spirits retailer, name withheld)</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Consumer products/retail (specialty beer, wine &amp; spirits retailer) - out of infra mandate</v>
+      </c>
+      <c r="H34" t="str">
+        <v>Rhode Island (Greater Providence area)</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Unknown (2025 SDE $318,372 stated, not EBITDA)</v>
+      </c>
+      <c r="J34" t="str">
+        <v>$2,455,930 (2025)</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L34" t="str">
+        <v>$1,250,000 + Inventory</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Retail (specialty beverage retail store, not infra service/O&amp;M or construction)</v>
+      </c>
+      <c r="N34" t="str">
+        <v>Unknown (credentialed retail staff mentioned; no CEO/CFO/ERP/systems detail stated)</v>
+      </c>
+      <c r="O34" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P34" t="str">
+        <v>Baystate Business Brokers</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>Single-listing broker blast (Listing #1917), no attachment/CIM/NDA mentioned in body; financials given as SDE (not EBITDA) plus 2025 revenue; "early access" window framed as one week for preferred buyers; contact Brian Labonte.</v>
+      </c>
+      <c r="R34">
+        <v>21</v>
+      </c>
+      <c r="S34" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T34" t="str">
+        <v>Specialty craft beer/wine/spirits retail store is a consumer products/retail brand with no infrastructure-operating character, so it is hard-disqualified under the rubric's consumer-brand exclusion (0/35 End-Market Fit) despite decent small-business fundamentals ($2.46M revenue, $318K SDE, $1.25M asking price).</v>
+      </c>
+      <c r="U34" t="str">
+        <v>N</v>
+      </c>
+      <c r="V34" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAEhx85wAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W34" t="str">
+        <v>New</v>
+      </c>
+      <c r="X34" t="str">
+        <v>&lt;2aa7e4ed-122c-5770-a94e-f90efa464f94@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y34" t="str">
+        <v>2026-09-09T15:52:00Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y33"/>
+  <autoFilter ref="A1:Y34"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y34"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y35</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y34"/>
+  <dimension ref="A1:Y35"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3047,10 +3047,87 @@
         <v>2026-09-09T15:52:00Z</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>DF-00034</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-09-10T14:55:02Z</v>
+      </c>
+      <c r="C35" t="str">
+        <v>New Listing 1922: Rare Opportunity: Thriving Absentee Owned Coastal Package Store with Prime Real Estate</v>
+      </c>
+      <c r="D35" t="str">
+        <v>admin@baystatebusinessbrokers.com</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Unnamed coastal package store (Listing 1922)</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Consumer retail (liquor/package store)</v>
+      </c>
+      <c r="H35" t="str">
+        <v>South Shore, MA (coastal, New England)</v>
+      </c>
+      <c r="I35" t="str">
+        <v>SDE 3-yr avg $109,456 (not EBITDA)</v>
+      </c>
+      <c r="J35" t="str">
+        <v>3-yr avg $788,974</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Business $550,000 + inventory; Real estate $1,200,000 (purchase or lease option)</v>
+      </c>
+      <c r="M35" t="str">
+        <v>Retail (wine, beer, spirits, micro-brewed beer, lottery, cigarettes/tobacco)</v>
+      </c>
+      <c r="N35" t="str">
+        <v>Unknown (currently absentee-owned)</v>
+      </c>
+      <c r="O35" t="str">
+        <v>N</v>
+      </c>
+      <c r="P35" t="str">
+        <v>BayState Business Brokers</v>
+      </c>
+      <c r="Q35" t="str">
+        <v>NDA available (click-to-sign); real estate included, purchase or lease option; absentee-owned turnkey listing.</v>
+      </c>
+      <c r="R35">
+        <v>8</v>
+      </c>
+      <c r="S35" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T35" t="str">
+        <v>Consumer retail liquor store with no infrastructure/asset-operating character and SDE well under $3M — hard-disqualified consumer products/brand, auto Pass regardless of other factors.</v>
+      </c>
+      <c r="U35" t="str">
+        <v>N</v>
+      </c>
+      <c r="V35" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAEhx85xAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W35" t="str">
+        <v>New</v>
+      </c>
+      <c r="X35" t="str">
+        <v>&lt;1bf0d73c-c2b5-5233-a13d-4297d1fd7c8f@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y35" t="str">
+        <v>2026-09-10T15:48:38Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y34"/>
+  <autoFilter ref="A1:Y35"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y34"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y35"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/XIP_Deal_Funnel_Intake.xlsx
+++ b/data/XIP_Deal_Funnel_Intake.xlsx
@@ -6,7 +6,7 @@
     <sheet name="Deal Funnel" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">'Deal Funnel'!A1:Y36</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y35"/>
+  <dimension ref="A1:Y36"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -3124,10 +3124,87 @@
         <v>2026-09-10T15:48:38Z</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>DF-00035</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2026-09-11T18:27:54Z</v>
+      </c>
+      <c r="C36" t="str">
+        <v>New Listing 1922: Rare Opportunity: Thriving Absentee Owned Coastal Package Store with Prime Real Estate</v>
+      </c>
+      <c r="D36" t="str">
+        <v>admin@baystatebusinessbrokers.com</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Broker</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Coastal Package Store (South Shore, MA)</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Consumer products/brands (retail liquor store)</v>
+      </c>
+      <c r="H36" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="J36" t="str">
+        <v>$788,974 (3-year average)</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Unknown (SDE $109,456 on 3-yr avg revenue; SDE, not EBITDA)</v>
+      </c>
+      <c r="L36" t="str">
+        <v>$550,000 business + $1,200,000 real estate (purchase or lease option available)</v>
+      </c>
+      <c r="M36" t="str">
+        <v>Retail (liquor/package store)</v>
+      </c>
+      <c r="N36" t="str">
+        <v>Unknown (currently absentee-owned)</v>
+      </c>
+      <c r="O36" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="P36" t="str">
+        <v>BayState Business Brokers</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>NDA required to access further info (link in email); real estate includes 3-bedroom apartment above store; purchase or lease option available on real estate.</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36" t="str">
+        <v>Pass</v>
+      </c>
+      <c r="T36" t="str">
+        <v>A retail liquor/package store is a consumer products/retail business with no infrastructure-operating character, hard-disqualifying it under the mandate regardless of its solid local financials.</v>
+      </c>
+      <c r="U36" t="str">
+        <v>N</v>
+      </c>
+      <c r="V36" t="str">
+        <v>https://outlook.office365.com/owa/?ItemID=AAMkAGJiZDg3MTI0LWFhNzUtNGQzYS1hNWQzLWZlNDVmMmExMzRkNgBGAAAAAAD9u3VVtvqtSpWuAIjP80zoBwB5X058TjLSTIlO61qPMaSdAAAAAAEMAAB5X058TjLSTIlO61qPMaSdAAEoLT2aAAA%3D&amp;exvsurl=1&amp;viewmodel=ReadMessageItem</v>
+      </c>
+      <c r="W36" t="str">
+        <v>New</v>
+      </c>
+      <c r="X36" t="str">
+        <v>&lt;a74361c9-d1a1-511f-89a8-0c32dbb81c03@pds.pdrserv.baystatebusinessbrokers.com&gt;</v>
+      </c>
+      <c r="Y36" t="str">
+        <v>2026-09-11T18:49:04Z</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Y35"/>
+  <autoFilter ref="A1:Y36"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Y36"/>
   </ignoredErrors>
 </worksheet>
 </file>